--- a/output/yearly_total_coral_cover_iteration_69_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_69_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.271133975308724</v>
+        <v>1.254738788647802</v>
       </c>
       <c r="C3" t="n">
-        <v>4.698199671875372</v>
+        <v>4.633973737063545</v>
       </c>
       <c r="D3" t="n">
-        <v>6.047354876338579</v>
+        <v>6.122311313557823</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01668852352267</v>
+        <v>12.01102383926917</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.425286317300714</v>
+        <v>1.393959719087991</v>
       </c>
       <c r="C4" t="n">
-        <v>5.315332232286419</v>
+        <v>5.152808983474919</v>
       </c>
       <c r="D4" t="n">
-        <v>6.340317793901347</v>
+        <v>6.459443174573454</v>
       </c>
       <c r="E4" t="n">
-        <v>13.08093634348848</v>
+        <v>13.00621187713636</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.634149842986658</v>
+        <v>1.58034566679985</v>
       </c>
       <c r="C5" t="n">
-        <v>6.147356086124399</v>
+        <v>5.809994749102803</v>
       </c>
       <c r="D5" t="n">
-        <v>6.790249493803966</v>
+        <v>6.830661436249713</v>
       </c>
       <c r="E5" t="n">
-        <v>14.57175542291502</v>
+        <v>14.22100185215237</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.864445017405101</v>
+        <v>1.789504363585277</v>
       </c>
       <c r="C6" t="n">
-        <v>7.153026541458306</v>
+        <v>6.615568244095629</v>
       </c>
       <c r="D6" t="n">
-        <v>7.131171874790264</v>
+        <v>7.219295040204053</v>
       </c>
       <c r="E6" t="n">
-        <v>16.14864343365367</v>
+        <v>15.62436764788496</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.124345746980306</v>
+        <v>2.019228367901718</v>
       </c>
       <c r="C7" t="n">
-        <v>8.348300021684274</v>
+        <v>7.537344171021657</v>
       </c>
       <c r="D7" t="n">
-        <v>7.542182100472338</v>
+        <v>7.633628075835621</v>
       </c>
       <c r="E7" t="n">
-        <v>18.01482786913692</v>
+        <v>17.190200614759</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.319895079180272</v>
+        <v>1.240784483726813</v>
       </c>
       <c r="C8" t="n">
-        <v>6.002174333703453</v>
+        <v>5.14360263411599</v>
       </c>
       <c r="D8" t="n">
-        <v>5.809940016126135</v>
+        <v>5.898048564809744</v>
       </c>
       <c r="E8" t="n">
-        <v>13.13200942900986</v>
+        <v>12.28243568265255</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.644771120750688</v>
+        <v>1.565945042131195</v>
       </c>
       <c r="C9" t="n">
-        <v>7.463282719611766</v>
+        <v>6.252092848052072</v>
       </c>
       <c r="D9" t="n">
-        <v>6.321652714931832</v>
+        <v>6.432201248584407</v>
       </c>
       <c r="E9" t="n">
-        <v>15.42970655529429</v>
+        <v>14.25023913876768</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.971215435242035</v>
+        <v>1.908495000411834</v>
       </c>
       <c r="C10" t="n">
-        <v>9.025999396675571</v>
+        <v>7.482121139034412</v>
       </c>
       <c r="D10" t="n">
-        <v>6.844435115496938</v>
+        <v>6.97196714002346</v>
       </c>
       <c r="E10" t="n">
-        <v>17.84164994741455</v>
+        <v>16.3625832794697</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.302215332490386</v>
+        <v>2.266655589236015</v>
       </c>
       <c r="C11" t="n">
-        <v>10.6233911582458</v>
+        <v>8.851579166046784</v>
       </c>
       <c r="D11" t="n">
-        <v>7.387423003562802</v>
+        <v>7.556940538248546</v>
       </c>
       <c r="E11" t="n">
-        <v>20.31302949429899</v>
+        <v>18.67517529353135</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.636070042731201</v>
+        <v>2.637653208102937</v>
       </c>
       <c r="C12" t="n">
-        <v>12.26697284385434</v>
+        <v>10.32028122372675</v>
       </c>
       <c r="D12" t="n">
-        <v>7.856837301432538</v>
+        <v>8.084166307234034</v>
       </c>
       <c r="E12" t="n">
-        <v>22.75988018801808</v>
+        <v>21.04210073906372</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.933542943186518</v>
+        <v>2.998267066243798</v>
       </c>
       <c r="C13" t="n">
-        <v>13.89285984122561</v>
+        <v>11.82107351463854</v>
       </c>
       <c r="D13" t="n">
-        <v>8.357031986481434</v>
+        <v>8.681005600028241</v>
       </c>
       <c r="E13" t="n">
-        <v>25.18343477089356</v>
+        <v>23.50034618091058</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.68449252842372</v>
+        <v>1.72685494186197</v>
       </c>
       <c r="C14" t="n">
-        <v>9.658944423186329</v>
+        <v>8.374101750207402</v>
       </c>
       <c r="D14" t="n">
-        <v>6.331556016567827</v>
+        <v>6.560941367665095</v>
       </c>
       <c r="E14" t="n">
-        <v>17.67499296817788</v>
+        <v>16.66189805973447</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.70919330066257</v>
+        <v>1.788086546175843</v>
       </c>
       <c r="C15" t="n">
-        <v>10.31202263100539</v>
+        <v>9.003873267527645</v>
       </c>
       <c r="D15" t="n">
-        <v>6.355579382890746</v>
+        <v>6.620877065009362</v>
       </c>
       <c r="E15" t="n">
-        <v>18.37679531455871</v>
+        <v>17.41283687871285</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.972409677648182</v>
+        <v>2.088422803859027</v>
       </c>
       <c r="C16" t="n">
-        <v>12.07157958889582</v>
+        <v>10.63157169126069</v>
       </c>
       <c r="D16" t="n">
-        <v>6.783385762493337</v>
+        <v>7.119604898766741</v>
       </c>
       <c r="E16" t="n">
-        <v>20.82737502903734</v>
+        <v>19.83959939388646</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.577020607239822</v>
+        <v>1.68616149952094</v>
       </c>
       <c r="C17" t="n">
-        <v>10.98606115231013</v>
+        <v>9.794435423849432</v>
       </c>
       <c r="D17" t="n">
-        <v>6.299600128794594</v>
+        <v>6.638126372172979</v>
       </c>
       <c r="E17" t="n">
-        <v>18.86268188834454</v>
+        <v>18.11872329554335</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.792524045799039</v>
+        <v>1.938667009053219</v>
       </c>
       <c r="C18" t="n">
-        <v>12.77527670834585</v>
+        <v>11.40309775959713</v>
       </c>
       <c r="D18" t="n">
-        <v>6.767383274914113</v>
+        <v>7.080727689678567</v>
       </c>
       <c r="E18" t="n">
-        <v>21.335184029059</v>
+        <v>20.42249245832891</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.792219704010722</v>
+        <v>1.961973699552038</v>
       </c>
       <c r="C19" t="n">
-        <v>13.61803839010244</v>
+        <v>12.18247780956754</v>
       </c>
       <c r="D19" t="n">
-        <v>6.862524444932673</v>
+        <v>7.207913104763743</v>
       </c>
       <c r="E19" t="n">
-        <v>22.27278253904583</v>
+        <v>21.35236461388332</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.984544079272672</v>
+        <v>2.203493452273797</v>
       </c>
       <c r="C20" t="n">
-        <v>15.65504706669006</v>
+        <v>13.9414162664043</v>
       </c>
       <c r="D20" t="n">
-        <v>7.267681904998287</v>
+        <v>7.637889146792719</v>
       </c>
       <c r="E20" t="n">
-        <v>24.90727305096102</v>
+        <v>23.78279886547082</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.172854712355494</v>
+        <v>1.32263995959243</v>
       </c>
       <c r="C21" t="n">
-        <v>11.56728524565536</v>
+        <v>10.21391658292001</v>
       </c>
       <c r="D21" t="n">
-        <v>6.062890939823645</v>
+        <v>6.37945548705803</v>
       </c>
       <c r="E21" t="n">
-        <v>18.8030308978345</v>
+        <v>17.91601202957047</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_69_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_69_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.254738788647802</v>
+        <v>1.27211572301297</v>
       </c>
       <c r="C3" t="n">
-        <v>4.633973737063545</v>
+        <v>4.613307947889151</v>
       </c>
       <c r="D3" t="n">
-        <v>6.122311313557823</v>
+        <v>6.06080481988676</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01102383926917</v>
+        <v>11.94622849078888</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.393959719087991</v>
+        <v>1.428155298037439</v>
       </c>
       <c r="C4" t="n">
-        <v>5.152808983474919</v>
+        <v>5.096829061339691</v>
       </c>
       <c r="D4" t="n">
-        <v>6.459443174573454</v>
+        <v>6.256026358946171</v>
       </c>
       <c r="E4" t="n">
-        <v>13.00621187713636</v>
+        <v>12.7810107183233</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.58034566679985</v>
+        <v>1.631609185739211</v>
       </c>
       <c r="C5" t="n">
-        <v>5.809994749102803</v>
+        <v>5.707113206893619</v>
       </c>
       <c r="D5" t="n">
-        <v>6.830661436249713</v>
+        <v>6.539987455064716</v>
       </c>
       <c r="E5" t="n">
-        <v>14.22100185215237</v>
+        <v>13.87870984769755</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.789504363585277</v>
+        <v>1.861554356557611</v>
       </c>
       <c r="C6" t="n">
-        <v>6.615568244095629</v>
+        <v>6.434013713034108</v>
       </c>
       <c r="D6" t="n">
-        <v>7.219295040204053</v>
+        <v>6.784486408823986</v>
       </c>
       <c r="E6" t="n">
-        <v>15.62436764788496</v>
+        <v>15.08005447841571</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.019228367901718</v>
+        <v>2.117629940006829</v>
       </c>
       <c r="C7" t="n">
-        <v>7.537344171021657</v>
+        <v>7.275205355939013</v>
       </c>
       <c r="D7" t="n">
-        <v>7.633628075835621</v>
+        <v>7.062779525724151</v>
       </c>
       <c r="E7" t="n">
-        <v>17.190200614759</v>
+        <v>16.45561482166999</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.240784483726813</v>
+        <v>1.323844016791206</v>
       </c>
       <c r="C8" t="n">
-        <v>5.14360263411599</v>
+        <v>4.891249077891836</v>
       </c>
       <c r="D8" t="n">
-        <v>5.898048564809744</v>
+        <v>5.299390493980595</v>
       </c>
       <c r="E8" t="n">
-        <v>12.28243568265255</v>
+        <v>11.51448358866364</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.565945042131195</v>
+        <v>1.675163636507114</v>
       </c>
       <c r="C9" t="n">
-        <v>6.252092848052072</v>
+        <v>5.94447795254278</v>
       </c>
       <c r="D9" t="n">
-        <v>6.432201248584407</v>
+        <v>5.692882953673107</v>
       </c>
       <c r="E9" t="n">
-        <v>14.25023913876768</v>
+        <v>13.312524542723</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.908495000411834</v>
+        <v>2.049176798838981</v>
       </c>
       <c r="C10" t="n">
-        <v>7.482121139034412</v>
+        <v>7.146706041008279</v>
       </c>
       <c r="D10" t="n">
-        <v>6.97196714002346</v>
+        <v>6.097030575696047</v>
       </c>
       <c r="E10" t="n">
-        <v>16.3625832794697</v>
+        <v>15.29291341554331</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.266655589236015</v>
+        <v>2.439967211186319</v>
       </c>
       <c r="C11" t="n">
-        <v>8.851579166046784</v>
+        <v>8.437262378099451</v>
       </c>
       <c r="D11" t="n">
-        <v>7.556940538248546</v>
+        <v>6.511694661515231</v>
       </c>
       <c r="E11" t="n">
-        <v>18.67517529353135</v>
+        <v>17.388924250801</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.637653208102937</v>
+        <v>2.865629207575532</v>
       </c>
       <c r="C12" t="n">
-        <v>10.32028122372675</v>
+        <v>9.888284351676667</v>
       </c>
       <c r="D12" t="n">
-        <v>8.084166307234034</v>
+        <v>6.943403204131899</v>
       </c>
       <c r="E12" t="n">
-        <v>21.04210073906372</v>
+        <v>19.6973167633841</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.998267066243798</v>
+        <v>3.280083412381281</v>
       </c>
       <c r="C13" t="n">
-        <v>11.82107351463854</v>
+        <v>11.40861262870471</v>
       </c>
       <c r="D13" t="n">
-        <v>8.681005600028241</v>
+        <v>7.481942305411065</v>
       </c>
       <c r="E13" t="n">
-        <v>23.50034618091058</v>
+        <v>22.17063834649706</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.72685494186197</v>
+        <v>1.908821878844116</v>
       </c>
       <c r="C14" t="n">
-        <v>8.374101750207402</v>
+        <v>8.125582136354364</v>
       </c>
       <c r="D14" t="n">
-        <v>6.560941367665095</v>
+        <v>5.727339391989127</v>
       </c>
       <c r="E14" t="n">
-        <v>16.66189805973447</v>
+        <v>15.76174340718761</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.788086546175843</v>
+        <v>1.977043526812227</v>
       </c>
       <c r="C15" t="n">
-        <v>9.003873267527645</v>
+        <v>8.796537969867762</v>
       </c>
       <c r="D15" t="n">
-        <v>6.620877065009362</v>
+        <v>5.716255460408181</v>
       </c>
       <c r="E15" t="n">
-        <v>17.41283687871285</v>
+        <v>16.48983695708817</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.088422803859027</v>
+        <v>2.317444908305724</v>
       </c>
       <c r="C16" t="n">
-        <v>10.63157169126069</v>
+        <v>10.43768633714899</v>
       </c>
       <c r="D16" t="n">
-        <v>7.119604898766741</v>
+        <v>6.152367425588698</v>
       </c>
       <c r="E16" t="n">
-        <v>19.83959939388646</v>
+        <v>18.90749867104341</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.68616149952094</v>
+        <v>1.867136871321797</v>
       </c>
       <c r="C17" t="n">
-        <v>9.794435423849432</v>
+        <v>9.667250008764258</v>
       </c>
       <c r="D17" t="n">
-        <v>6.638126372172979</v>
+        <v>5.703492740252972</v>
       </c>
       <c r="E17" t="n">
-        <v>18.11872329554335</v>
+        <v>17.23787962033903</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.938667009053219</v>
+        <v>2.144618042450115</v>
       </c>
       <c r="C18" t="n">
-        <v>11.40309775959713</v>
+        <v>11.30350927247833</v>
       </c>
       <c r="D18" t="n">
-        <v>7.080727689678567</v>
+        <v>6.085402414682024</v>
       </c>
       <c r="E18" t="n">
-        <v>20.42249245832891</v>
+        <v>19.53352972961047</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.961973699552038</v>
+        <v>2.164243179058009</v>
       </c>
       <c r="C19" t="n">
-        <v>12.18247780956754</v>
+        <v>12.1046546690519</v>
       </c>
       <c r="D19" t="n">
-        <v>7.207913104763743</v>
+        <v>6.162832856115971</v>
       </c>
       <c r="E19" t="n">
-        <v>21.35236461388332</v>
+        <v>20.43173070422588</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.203493452273797</v>
+        <v>2.433055517957828</v>
       </c>
       <c r="C20" t="n">
-        <v>13.9414162664043</v>
+        <v>13.94014981186582</v>
       </c>
       <c r="D20" t="n">
-        <v>7.637889146792719</v>
+        <v>6.562895045596546</v>
       </c>
       <c r="E20" t="n">
-        <v>23.78279886547082</v>
+        <v>22.9361003754202</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.32263995959243</v>
+        <v>1.45835676222751</v>
       </c>
       <c r="C21" t="n">
-        <v>10.21391658292001</v>
+        <v>10.27739638947661</v>
       </c>
       <c r="D21" t="n">
-        <v>6.37945548705803</v>
+        <v>5.460009492122721</v>
       </c>
       <c r="E21" t="n">
-        <v>17.91601202957047</v>
+        <v>17.19576264382684</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_69_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_69_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.27211572301297</v>
+        <v>2.601866557586597</v>
       </c>
       <c r="C3" t="n">
-        <v>4.613307947889151</v>
+        <v>7.658355755782769</v>
       </c>
       <c r="D3" t="n">
-        <v>6.06080481988676</v>
+        <v>8.174608421761871</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94622849078888</v>
+        <v>18.43483073513124</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.428155298037439</v>
+        <v>1.1034129031853</v>
       </c>
       <c r="C4" t="n">
-        <v>5.096829061339691</v>
+        <v>4.359948155727178</v>
       </c>
       <c r="D4" t="n">
-        <v>6.256026358946171</v>
+        <v>5.775082251075198</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7810107183233</v>
+        <v>11.23844330998768</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.631609185739211</v>
+        <v>1.23424401369569</v>
       </c>
       <c r="C5" t="n">
-        <v>5.707113206893619</v>
+        <v>4.830392043139135</v>
       </c>
       <c r="D5" t="n">
-        <v>6.539987455064716</v>
+        <v>6.123921647242018</v>
       </c>
       <c r="E5" t="n">
-        <v>13.87870984769755</v>
+        <v>12.18855770407684</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.861554356557611</v>
+        <v>1.391856328610802</v>
       </c>
       <c r="C6" t="n">
-        <v>6.434013713034108</v>
+        <v>5.400944318181304</v>
       </c>
       <c r="D6" t="n">
-        <v>6.784486408823986</v>
+        <v>6.458804134985765</v>
       </c>
       <c r="E6" t="n">
-        <v>15.08005447841571</v>
+        <v>13.25160478177787</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.117629940006829</v>
+        <v>1.568830602903271</v>
       </c>
       <c r="C7" t="n">
-        <v>7.275205355939013</v>
+        <v>6.088765552154327</v>
       </c>
       <c r="D7" t="n">
-        <v>7.062779525724151</v>
+        <v>6.866794578291802</v>
       </c>
       <c r="E7" t="n">
-        <v>16.45561482166999</v>
+        <v>14.5243907333494</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.323844016791206</v>
+        <v>1.765333709630262</v>
       </c>
       <c r="C8" t="n">
-        <v>4.891249077891836</v>
+        <v>6.881404046435743</v>
       </c>
       <c r="D8" t="n">
-        <v>5.299390493980595</v>
+        <v>7.356437825010436</v>
       </c>
       <c r="E8" t="n">
-        <v>11.51448358866364</v>
+        <v>16.00317558107644</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.675163636507114</v>
+        <v>1.967477986335996</v>
       </c>
       <c r="C9" t="n">
-        <v>5.94447795254278</v>
+        <v>7.786280310862453</v>
       </c>
       <c r="D9" t="n">
-        <v>5.692882953673107</v>
+        <v>7.875500595698183</v>
       </c>
       <c r="E9" t="n">
-        <v>13.312524542723</v>
+        <v>17.62925889289663</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.049176798838981</v>
+        <v>1.205988697373825</v>
       </c>
       <c r="C10" t="n">
-        <v>7.146706041008279</v>
+        <v>5.918387495235556</v>
       </c>
       <c r="D10" t="n">
-        <v>6.097030575696047</v>
+        <v>6.234657518158666</v>
       </c>
       <c r="E10" t="n">
-        <v>15.29291341554331</v>
+        <v>13.35903371076805</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.439967211186319</v>
+        <v>1.182976531186279</v>
       </c>
       <c r="C11" t="n">
-        <v>8.437262378099451</v>
+        <v>6.07047003210043</v>
       </c>
       <c r="D11" t="n">
-        <v>6.511694661515231</v>
+        <v>6.169047319083853</v>
       </c>
       <c r="E11" t="n">
-        <v>17.388924250801</v>
+        <v>13.42249388237056</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.865629207575532</v>
+        <v>1.318516619234594</v>
       </c>
       <c r="C12" t="n">
-        <v>9.888284351676667</v>
+        <v>7.041251614490803</v>
       </c>
       <c r="D12" t="n">
-        <v>6.943403204131899</v>
+        <v>6.617931821896621</v>
       </c>
       <c r="E12" t="n">
-        <v>19.6973167633841</v>
+        <v>14.97770005562202</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.280083412381281</v>
+        <v>1.063674550166207</v>
       </c>
       <c r="C13" t="n">
-        <v>11.40861262870471</v>
+        <v>6.628063458204449</v>
       </c>
       <c r="D13" t="n">
-        <v>7.481942305411065</v>
+        <v>6.101041655610675</v>
       </c>
       <c r="E13" t="n">
-        <v>22.17063834649706</v>
+        <v>13.79277966398133</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.908821878844116</v>
+        <v>1.184684772191669</v>
       </c>
       <c r="C14" t="n">
-        <v>8.125582136354364</v>
+        <v>7.672309221303611</v>
       </c>
       <c r="D14" t="n">
-        <v>5.727339391989127</v>
+        <v>6.521730364357477</v>
       </c>
       <c r="E14" t="n">
-        <v>15.76174340718761</v>
+        <v>15.37872435785276</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.977043526812227</v>
+        <v>1.18051234444862</v>
       </c>
       <c r="C15" t="n">
-        <v>8.796537969867762</v>
+        <v>8.214832820147441</v>
       </c>
       <c r="D15" t="n">
-        <v>5.716255460408181</v>
+        <v>6.629526262283776</v>
       </c>
       <c r="E15" t="n">
-        <v>16.48983695708817</v>
+        <v>16.02487142687984</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.317444908305724</v>
+        <v>1.321923283768331</v>
       </c>
       <c r="C16" t="n">
-        <v>10.43768633714899</v>
+        <v>9.576241996580578</v>
       </c>
       <c r="D16" t="n">
-        <v>6.152367425588698</v>
+        <v>7.191400108378311</v>
       </c>
       <c r="E16" t="n">
-        <v>18.90749867104341</v>
+        <v>18.08956538872722</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.867136871321797</v>
+        <v>0.8008803246934205</v>
       </c>
       <c r="C17" t="n">
-        <v>9.667250008764258</v>
+        <v>7.247114290594316</v>
       </c>
       <c r="D17" t="n">
-        <v>5.703492740252972</v>
+        <v>6.046957174583719</v>
       </c>
       <c r="E17" t="n">
-        <v>17.23787962033903</v>
+        <v>14.09495178987146</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.144618042450115</v>
+        <v>0.6524498892883452</v>
       </c>
       <c r="C18" t="n">
-        <v>11.30350927247833</v>
+        <v>6.27440848270362</v>
       </c>
       <c r="D18" t="n">
-        <v>6.085402414682024</v>
+        <v>5.583896234921626</v>
       </c>
       <c r="E18" t="n">
-        <v>19.53352972961047</v>
+        <v>12.51075460691359</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.164243179058009</v>
+        <v>0.7797040267128169</v>
       </c>
       <c r="C19" t="n">
-        <v>12.1046546690519</v>
+        <v>7.701516215504955</v>
       </c>
       <c r="D19" t="n">
-        <v>6.162832856115971</v>
+        <v>6.223956468182377</v>
       </c>
       <c r="E19" t="n">
-        <v>20.43173070422588</v>
+        <v>14.70517671040015</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.433055517957828</v>
+        <v>0.9103059238087698</v>
       </c>
       <c r="C20" t="n">
-        <v>13.94014981186582</v>
+        <v>9.228889841341013</v>
       </c>
       <c r="D20" t="n">
-        <v>6.562895045596546</v>
+        <v>6.887549193913923</v>
       </c>
       <c r="E20" t="n">
-        <v>22.9361003754202</v>
+        <v>17.02674495906371</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.45835676222751</v>
+        <v>1.03870870604721</v>
       </c>
       <c r="C21" t="n">
-        <v>10.27739638947661</v>
+        <v>10.818663351259</v>
       </c>
       <c r="D21" t="n">
-        <v>5.460009492122721</v>
+        <v>7.500356110904782</v>
       </c>
       <c r="E21" t="n">
-        <v>17.19576264382684</v>
+        <v>19.35772816821099</v>
       </c>
     </row>
   </sheetData>
